--- a/docs/reports/daily/WR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/WR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,6 +309,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -714,7 +732,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -857,19 +874,19 @@
         <f>'Daily Breakdown'!J49</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="46">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="47">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="48">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="47">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -877,19 +894,19 @@
         <f>'Daily Breakdown'!K49</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="46">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="47">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="47">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="48">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -939,7 +956,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed below; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1011,7 +1034,7 @@
       <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1051,7 +1074,7 @@
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1091,7 +1114,7 @@
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1131,7 +1154,7 @@
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1171,7 +1194,7 @@
       <c r="C8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="49" t="n">
         <v>88.94</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1211,7 +1234,7 @@
       <c r="C9" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1251,7 +1274,7 @@
       <c r="C10" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1291,7 +1314,7 @@
       <c r="C11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1331,7 +1354,7 @@
       <c r="C12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1371,7 +1394,7 @@
       <c r="C13" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="49" t="n">
         <v>93.87</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1411,7 +1434,7 @@
       <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1451,7 +1474,7 @@
       <c r="C15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="49" t="n">
         <v>93.86</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1491,7 +1514,7 @@
       <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1531,7 +1554,7 @@
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="49" t="n">
         <v>93.31999999999999</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1571,7 +1594,7 @@
       <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="49" t="n">
         <v>93.91</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1611,7 +1634,7 @@
       <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1651,7 +1674,7 @@
       <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="49" t="n">
         <v>93.81999999999999</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1691,7 +1714,7 @@
       <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="49" t="n">
         <v>93.89</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1731,7 +1754,7 @@
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1771,7 +1794,7 @@
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="49" t="n">
         <v>93.84999999999999</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1811,7 +1834,7 @@
       <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="49" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1851,7 +1874,7 @@
       <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="49" t="n">
         <v>90.88</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1891,7 +1914,7 @@
       <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="49" t="n">
         <v>93.88</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1931,7 +1954,7 @@
       <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="49" t="n">
         <v>91.47</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1971,7 +1994,7 @@
       <c r="C28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="49" t="n">
         <v>44.3</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2011,7 +2034,7 @@
       <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="49" t="n">
         <v>51.69</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2051,7 +2074,7 @@
       <c r="C30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="49" t="n">
         <v>84.33</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2091,7 +2114,7 @@
       <c r="C31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="49" t="n">
         <v>85.88</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2131,7 +2154,7 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="49" t="n">
         <v>40.53</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2171,7 +2194,7 @@
       <c r="C33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="49" t="n">
         <v>59.14</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2211,7 +2234,7 @@
       <c r="C34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="49" t="n">
         <v>36.87</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2251,7 +2274,7 @@
       <c r="C35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="49" t="n">
         <v>51.65</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2291,7 +2314,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="49" t="n">
         <v>40.98</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2331,7 +2354,7 @@
       <c r="C37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="49" t="n">
         <v>33.97</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2371,7 +2394,7 @@
       <c r="C38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="49" t="n">
         <v>53.28</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2411,7 +2434,7 @@
       <c r="C39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="49" t="n">
         <v>17.12</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2451,7 +2474,7 @@
       <c r="C40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="49" t="n">
         <v>53.17</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2491,7 +2514,7 @@
       <c r="C41" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="49" t="n">
         <v>36.89</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2531,7 +2554,7 @@
       <c r="C42" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="49" t="n">
         <v>36.99</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2571,7 +2594,7 @@
       <c r="C43" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="49" t="n">
         <v>1.98</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2611,7 +2634,7 @@
       <c r="C44" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="17" t="n">
+      <c r="D44" s="49" t="n">
         <v>36.8</v>
       </c>
       <c r="E44" s="18" t="n">
@@ -2651,7 +2674,7 @@
       <c r="C45" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="17" t="n">
+      <c r="D45" s="49" t="n">
         <v>36.87</v>
       </c>
       <c r="E45" s="18" t="n">
@@ -2691,7 +2714,7 @@
       <c r="C46" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="17" t="n">
+      <c r="D46" s="49" t="n">
         <v>34.14</v>
       </c>
       <c r="E46" s="18" t="n">
@@ -2731,7 +2754,7 @@
       <c r="C47" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="17" t="n">
+      <c r="D47" s="49" t="n">
         <v>36.7</v>
       </c>
       <c r="E47" s="18" t="n">
@@ -2772,7 +2795,7 @@
         <f>SUM(C4:C47)</f>
         <v/>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="50">
         <f>SUM(D4:D47)</f>
         <v/>
       </c>
@@ -2781,7 +2804,7 @@
         <v/>
       </c>
       <c r="F48" s="23">
-        <f>SUM(F4:F47)</f>
+        <f>SUMIF(E4:E47,"&gt;0",F4:F47)</f>
         <v/>
       </c>
       <c r="G48" s="24">
@@ -2816,7 +2839,7 @@
         <f>C48</f>
         <v/>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="51">
         <f>D48</f>
         <v/>
       </c>
@@ -2892,7 +2915,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -2900,7 +2922,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -10468,7 +10489,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -13407,7 +13427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -13422,7 +13442,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="44" t="inlineStr">
         <is>

--- a/docs/reports/daily/WR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/WR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3419,7 +3419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3497,6 +3497,11 @@
           <t>Valid Trip?</t>
         </is>
       </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Loco Travel</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
@@ -3553,6 +3558,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -3609,6 +3615,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -3665,6 +3672,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -3721,6 +3729,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -3777,6 +3786,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -3833,6 +3843,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
@@ -3889,6 +3900,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -3945,6 +3957,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4001,6 +4014,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4057,6 +4071,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4113,6 +4128,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4169,6 +4185,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4225,6 +4242,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
@@ -4281,6 +4299,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4337,6 +4356,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4393,6 +4413,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -4449,6 +4470,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -4505,6 +4527,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -4561,6 +4584,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -4673,6 +4698,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -4729,6 +4755,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -4785,6 +4812,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -4841,6 +4869,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
@@ -4897,6 +4926,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -4953,6 +4983,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -5009,6 +5040,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -5065,6 +5097,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -5121,6 +5154,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -5177,6 +5211,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
@@ -5233,6 +5268,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -5289,6 +5325,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -5345,6 +5382,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -5401,6 +5439,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -5457,6 +5496,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -5513,6 +5553,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -5569,6 +5610,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -5625,6 +5667,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -5681,6 +5724,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -5737,6 +5781,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -5793,6 +5838,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -5849,6 +5895,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -5905,6 +5952,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -5961,6 +6009,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -6017,6 +6066,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M50" s="16" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -6073,6 +6123,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -6129,6 +6180,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -6185,6 +6237,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -6241,6 +6294,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -6297,6 +6351,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -6353,6 +6408,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
@@ -6409,6 +6465,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -6465,6 +6522,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M58" s="16" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -6521,6 +6579,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -6577,6 +6636,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -6633,6 +6693,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -6689,6 +6750,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -6745,6 +6807,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -6801,6 +6864,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -6857,6 +6921,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
@@ -6913,6 +6978,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -6969,6 +7035,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -7025,6 +7092,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -7081,6 +7149,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -7137,6 +7206,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -7193,6 +7263,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M71" s="16" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
@@ -7249,6 +7320,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M72" s="16" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -7305,6 +7377,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -7361,6 +7434,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -7417,6 +7491,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -7473,6 +7548,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -7529,6 +7605,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -7585,6 +7662,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M78" s="16" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -7641,6 +7719,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M79" s="16" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
@@ -7697,6 +7776,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M80" s="16" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -7753,6 +7833,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -7809,6 +7890,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -7865,6 +7947,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -7921,6 +8004,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M84" s="16" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -7977,6 +8061,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M85" s="16" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
@@ -8033,6 +8118,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M86" s="16" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -8089,6 +8175,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M87" s="16" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
@@ -8145,6 +8232,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
@@ -8201,6 +8289,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
@@ -8257,6 +8346,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M90" s="16" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
@@ -8313,6 +8403,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M91" s="16" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
@@ -8369,6 +8460,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M92" s="16" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
@@ -8425,6 +8517,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M93" s="16" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
@@ -8481,6 +8574,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M94" s="16" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
@@ -8537,6 +8631,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M95" s="16" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
@@ -8593,6 +8688,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M96" s="16" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
@@ -8649,6 +8745,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M97" s="16" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="31" t="inlineStr">
@@ -8705,6 +8802,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M98" s="16" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="31" t="inlineStr">
@@ -8761,6 +8859,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M99" s="16" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="31" t="inlineStr">
@@ -8817,6 +8916,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M100" s="16" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
@@ -8873,6 +8973,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M101" s="16" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="16" t="inlineStr">
@@ -8929,6 +9030,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M102" s="16" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
@@ -8985,6 +9087,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M103" s="16" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="16" t="inlineStr">
@@ -9041,6 +9144,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M104" s="16" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
@@ -9097,6 +9201,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M105" s="16" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="16" t="inlineStr">
@@ -9153,6 +9258,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M106" s="16" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
@@ -9209,6 +9315,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M107" s="16" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
@@ -9265,6 +9372,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M108" s="16" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
@@ -9321,6 +9429,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M109" s="16" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
@@ -9377,6 +9486,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M110" s="16" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
@@ -9433,6 +9543,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M111" s="16" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
@@ -9489,6 +9600,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M112" s="16" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
@@ -9545,6 +9657,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M113" s="16" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="31" t="inlineStr">
@@ -9601,6 +9714,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M114" s="16" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="31" t="inlineStr">
@@ -9657,6 +9771,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M115" s="16" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="31" t="inlineStr">
@@ -9713,6 +9828,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M116" s="16" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="31" t="inlineStr">
@@ -9769,6 +9885,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M117" s="16" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
@@ -9825,6 +9942,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M118" s="16" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="31" t="inlineStr">
@@ -9881,6 +9999,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M119" s="16" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="31" t="inlineStr">
@@ -9937,6 +10056,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M120" s="16" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="31" t="inlineStr">
@@ -9993,6 +10113,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M121" s="16" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="31" t="inlineStr">
@@ -10049,6 +10170,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M122" s="16" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="31" t="inlineStr">
@@ -10105,6 +10227,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M123" s="16" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="31" t="inlineStr">
@@ -10161,6 +10284,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M124" s="16" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="31" t="inlineStr">
@@ -10217,6 +10341,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M125" s="16" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="31" t="inlineStr">
@@ -10273,6 +10398,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M126" s="16" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="31" t="inlineStr">
@@ -10329,6 +10455,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M127" s="16" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="31" t="inlineStr">
@@ -10385,6 +10512,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M128" s="16" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="31" t="inlineStr">
@@ -10441,6 +10569,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M129" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/reports/daily/WR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/WR_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -3558,7 +3558,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -3615,7 +3619,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -3672,7 +3680,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -3729,7 +3741,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -3786,7 +3802,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -3843,7 +3863,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
@@ -3900,7 +3924,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -3957,7 +3985,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4014,7 +4046,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4071,7 +4107,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4128,7 +4168,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M16" s="16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4185,7 +4229,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4242,7 +4290,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
@@ -4299,7 +4351,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4356,7 +4412,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4413,7 +4473,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -4470,7 +4534,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -4527,7 +4595,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -4584,7 +4656,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -4641,7 +4717,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -4698,7 +4778,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M26" s="16" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -4755,7 +4839,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -4812,7 +4900,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M28" s="16" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -4869,7 +4961,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M29" s="16" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
@@ -4926,7 +5022,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M30" s="16" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -4983,7 +5083,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M31" s="16" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -5040,7 +5144,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M32" s="16" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -5097,7 +5205,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M33" s="16" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -5154,7 +5266,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M34" s="16" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -5211,7 +5327,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M35" s="16" t="inlineStr"/>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
@@ -5268,7 +5388,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M36" s="16" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -5325,7 +5449,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M37" s="16" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -5382,7 +5510,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M38" s="16" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -5439,7 +5571,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M39" s="16" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -5496,7 +5632,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M40" s="16" t="inlineStr"/>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -5553,7 +5693,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M41" s="16" t="inlineStr"/>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -5610,7 +5754,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M42" s="16" t="inlineStr"/>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -5667,7 +5815,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M43" s="16" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -5724,7 +5876,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M44" s="16" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -5781,7 +5937,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M45" s="16" t="inlineStr"/>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -5838,7 +5998,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M46" s="16" t="inlineStr"/>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -5895,7 +6059,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M47" s="16" t="inlineStr"/>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -5952,7 +6120,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M48" s="16" t="inlineStr"/>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -6009,7 +6181,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M49" s="16" t="inlineStr"/>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -6066,7 +6242,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M50" s="16" t="inlineStr"/>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -6123,7 +6303,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M51" s="16" t="inlineStr"/>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -6180,7 +6364,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M52" s="16" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -6237,7 +6425,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M53" s="16" t="inlineStr"/>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -6294,7 +6486,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M54" s="16" t="inlineStr"/>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -6351,7 +6547,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M55" s="16" t="inlineStr"/>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -6408,7 +6608,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M56" s="16" t="inlineStr"/>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
@@ -6465,7 +6669,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M57" s="16" t="inlineStr"/>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -6522,7 +6730,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M58" s="16" t="inlineStr"/>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -6579,7 +6791,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M59" s="16" t="inlineStr"/>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -6636,7 +6852,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M60" s="16" t="inlineStr"/>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -6693,7 +6913,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M61" s="16" t="inlineStr"/>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -6750,7 +6974,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M62" s="16" t="inlineStr"/>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -6807,7 +7035,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M63" s="16" t="inlineStr"/>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -6864,7 +7096,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M64" s="16" t="inlineStr"/>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -6921,7 +7157,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M65" s="16" t="inlineStr"/>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
@@ -6978,7 +7218,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M66" s="16" t="inlineStr"/>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -7035,7 +7279,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M67" s="16" t="inlineStr"/>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -7092,7 +7340,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M68" s="16" t="inlineStr"/>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -7149,7 +7401,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M69" s="16" t="inlineStr"/>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -7206,7 +7462,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M70" s="16" t="inlineStr"/>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -7263,7 +7523,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M71" s="16" t="inlineStr"/>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
@@ -7320,7 +7584,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M72" s="16" t="inlineStr"/>
+      <c r="M72" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -7377,7 +7645,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M73" s="16" t="inlineStr"/>
+      <c r="M73" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -7434,7 +7706,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M74" s="16" t="inlineStr"/>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -7491,7 +7767,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M75" s="16" t="inlineStr"/>
+      <c r="M75" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -7548,7 +7828,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M76" s="16" t="inlineStr"/>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -7605,7 +7889,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M77" s="16" t="inlineStr"/>
+      <c r="M77" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -7662,7 +7950,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M78" s="16" t="inlineStr"/>
+      <c r="M78" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -7719,7 +8011,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M79" s="16" t="inlineStr"/>
+      <c r="M79" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
@@ -7776,7 +8072,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M80" s="16" t="inlineStr"/>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -7833,7 +8133,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M81" s="16" t="inlineStr"/>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -7890,7 +8194,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M82" s="16" t="inlineStr"/>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -7947,7 +8255,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M83" s="16" t="inlineStr"/>
+      <c r="M83" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -8004,7 +8316,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M84" s="16" t="inlineStr"/>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -8061,7 +8377,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M85" s="16" t="inlineStr"/>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
@@ -8118,7 +8438,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M86" s="16" t="inlineStr"/>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -8175,7 +8499,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M87" s="16" t="inlineStr"/>
+      <c r="M87" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
@@ -8232,7 +8560,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M88" s="16" t="inlineStr"/>
+      <c r="M88" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
@@ -8289,7 +8621,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M89" s="16" t="inlineStr"/>
+      <c r="M89" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
@@ -8346,7 +8682,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M90" s="16" t="inlineStr"/>
+      <c r="M90" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
@@ -8403,7 +8743,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M91" s="16" t="inlineStr"/>
+      <c r="M91" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
@@ -8460,7 +8804,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M92" s="16" t="inlineStr"/>
+      <c r="M92" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
@@ -8517,7 +8865,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M93" s="16" t="inlineStr"/>
+      <c r="M93" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
@@ -8574,7 +8926,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M94" s="16" t="inlineStr"/>
+      <c r="M94" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
@@ -8631,7 +8987,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M95" s="16" t="inlineStr"/>
+      <c r="M95" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
@@ -8688,7 +9048,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M96" s="16" t="inlineStr"/>
+      <c r="M96" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
@@ -8745,7 +9109,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M97" s="16" t="inlineStr"/>
+      <c r="M97" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="31" t="inlineStr">
@@ -8802,7 +9170,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M98" s="16" t="inlineStr"/>
+      <c r="M98" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="31" t="inlineStr">
@@ -8859,7 +9231,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M99" s="16" t="inlineStr"/>
+      <c r="M99" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="31" t="inlineStr">
@@ -8916,7 +9292,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M100" s="16" t="inlineStr"/>
+      <c r="M100" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
@@ -8973,7 +9353,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M101" s="16" t="inlineStr"/>
+      <c r="M101" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="16" t="inlineStr">
@@ -9030,7 +9414,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M102" s="16" t="inlineStr"/>
+      <c r="M102" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
@@ -9087,7 +9475,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M103" s="16" t="inlineStr"/>
+      <c r="M103" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="16" t="inlineStr">
@@ -9144,7 +9536,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M104" s="16" t="inlineStr"/>
+      <c r="M104" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
@@ -9201,7 +9597,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M105" s="16" t="inlineStr"/>
+      <c r="M105" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="16" t="inlineStr">
@@ -9258,7 +9658,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M106" s="16" t="inlineStr"/>
+      <c r="M106" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
@@ -9315,7 +9719,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M107" s="16" t="inlineStr"/>
+      <c r="M107" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
@@ -9372,7 +9780,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M108" s="16" t="inlineStr"/>
+      <c r="M108" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
@@ -9429,7 +9841,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M109" s="16" t="inlineStr"/>
+      <c r="M109" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
@@ -9486,7 +9902,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M110" s="16" t="inlineStr"/>
+      <c r="M110" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
@@ -9543,7 +9963,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M111" s="16" t="inlineStr"/>
+      <c r="M111" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
@@ -9600,7 +10024,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M112" s="16" t="inlineStr"/>
+      <c r="M112" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
@@ -9657,7 +10085,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M113" s="16" t="inlineStr"/>
+      <c r="M113" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="31" t="inlineStr">
@@ -9714,7 +10146,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M114" s="16" t="inlineStr"/>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="31" t="inlineStr">
@@ -9771,7 +10207,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M115" s="16" t="inlineStr"/>
+      <c r="M115" s="16" t="inlineStr">
+        <is>
+          <t>LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="31" t="inlineStr">
@@ -9828,7 +10268,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M116" s="16" t="inlineStr"/>
+      <c r="M116" s="16" t="inlineStr">
+        <is>
+          <t>LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="31" t="inlineStr">
@@ -9885,7 +10329,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M117" s="16" t="inlineStr"/>
+      <c r="M117" s="16" t="inlineStr">
+        <is>
+          <t>LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
@@ -9942,7 +10390,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M118" s="16" t="inlineStr"/>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="31" t="inlineStr">
@@ -9999,7 +10451,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M119" s="16" t="inlineStr"/>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="31" t="inlineStr">
@@ -10056,7 +10512,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M120" s="16" t="inlineStr"/>
+      <c r="M120" s="16" t="inlineStr">
+        <is>
+          <t>UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="31" t="inlineStr">
@@ -10113,7 +10573,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M121" s="16" t="inlineStr"/>
+      <c r="M121" s="16" t="inlineStr">
+        <is>
+          <t>UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="31" t="inlineStr">
@@ -10170,7 +10634,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M122" s="16" t="inlineStr"/>
+      <c r="M122" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="31" t="inlineStr">
@@ -10227,7 +10695,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M123" s="16" t="inlineStr"/>
+      <c r="M123" s="16" t="inlineStr">
+        <is>
+          <t>UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="31" t="inlineStr">
@@ -10284,7 +10756,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M124" s="16" t="inlineStr"/>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="31" t="inlineStr">
@@ -10341,7 +10817,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M125" s="16" t="inlineStr"/>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="31" t="inlineStr">
@@ -10398,7 +10878,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M126" s="16" t="inlineStr"/>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="31" t="inlineStr">
@@ -10455,7 +10939,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M127" s="16" t="inlineStr"/>
+      <c r="M127" s="16" t="inlineStr">
+        <is>
+          <t>BAREJADI NANDEJ, GERATPUR, VATVA, KANKARIYA CABIN, AHMEDABAD Jn</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="31" t="inlineStr">
@@ -10512,7 +11000,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M128" s="16" t="inlineStr"/>
+      <c r="M128" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="31" t="inlineStr">
@@ -10569,7 +11061,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M129" s="16" t="inlineStr"/>
+      <c r="M129" s="16" t="inlineStr">
+        <is>
+          <t>BAJWA, RANOLI, LC-246, VASAD, ADAS ROAD, VADOD, LC-258, ANAND Jn, LC-264, KANJARI BORIYAVI, UTARSANDA, NADIAD, LC-278, GOTHAJ, LC-286, MAHEMDABAD AND KHEDA ROAD, LC-294, KANIJ, BAREJADI NANDEJ, GERATPUR, VATVA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
